--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016321</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137016314</v>
       </c>
       <c r="B3" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137016319</v>
       </c>
       <c r="B4" t="n">
-        <v>92076</v>
+        <v>92078</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137016313</v>
       </c>
       <c r="B5" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137016315</v>
       </c>
       <c r="B6" t="n">
-        <v>80591</v>
+        <v>80595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>137016317</v>
       </c>
       <c r="B10" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>137016322</v>
       </c>
       <c r="B11" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137016355</v>
       </c>
       <c r="B12" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>137016357</v>
       </c>
       <c r="B13" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016321</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137016314</v>
       </c>
       <c r="B3" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137016319</v>
       </c>
       <c r="B4" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137016313</v>
       </c>
       <c r="B5" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137016315</v>
       </c>
       <c r="B6" t="n">
-        <v>80595</v>
+        <v>80597</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>137016317</v>
       </c>
       <c r="B10" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>137016322</v>
       </c>
       <c r="B11" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137016355</v>
       </c>
       <c r="B12" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>137016357</v>
       </c>
       <c r="B13" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137016321</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137016314</v>
       </c>
       <c r="B3" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137016319</v>
       </c>
       <c r="B4" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137016313</v>
       </c>
       <c r="B5" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137016315</v>
       </c>
       <c r="B6" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>137016317</v>
       </c>
       <c r="B10" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         <v>137016322</v>
       </c>
       <c r="B11" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137016355</v>
       </c>
       <c r="B12" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
         <v>137016357</v>
       </c>
       <c r="B13" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ13"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>137016321</v>
+        <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92395</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>637350</v>
+        <v>637354</v>
       </c>
       <c r="R2" t="n">
-        <v>7012755</v>
+        <v>7012984</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,22 +745,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,22 +780,22 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016321</t>
+          <t>https://artportalen.se/Sighting/137124361</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>137016314</v>
+        <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92139</v>
+        <v>92395</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>637421</v>
+        <v>637370</v>
       </c>
       <c r="R3" t="n">
-        <v>7012891</v>
+        <v>7012821</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -857,22 +857,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:56</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,60 +892,63 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016314</t>
+          <t>https://artportalen.se/Sighting/137124366</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137016319</v>
+        <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92081</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>637357</v>
+        <v>637343</v>
       </c>
       <c r="R4" t="n">
-        <v>7012776</v>
+        <v>7012976</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,71 +996,84 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016319</t>
+          <t>https://artportalen.se/Sighting/137132761</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>137016313</v>
+        <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>79483</v>
+        <v>92124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>637421</v>
+        <v>637350</v>
       </c>
       <c r="R5" t="n">
-        <v>7012891</v>
+        <v>7012755</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1089,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,24 +1124,8 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1141,16 +1141,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016313</t>
+          <t>https://artportalen.se/Sighting/137016321</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>137016315</v>
+        <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>80598</v>
+        <v>92124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,41 +1158,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>637352</v>
+        <v>637351</v>
       </c>
       <c r="R6" t="n">
-        <v>7012807</v>
+        <v>7012926</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1219,22 +1212,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,24 +1236,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1270,65 +1247,57 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016315</t>
+          <t>https://artportalen.se/Sighting/137124358</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>137016320</v>
+        <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>58005</v>
+        <v>92124</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>637351</v>
+        <v>637371</v>
       </c>
       <c r="R7" t="n">
-        <v>7012753</v>
+        <v>7012830</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1355,22 +1324,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,22 +1359,22 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016320</t>
+          <t>https://artportalen.se/Sighting/137124365</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>137016324</v>
+        <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>58169</v>
+        <v>92124</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1413,53 +1382,40 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>637373</v>
+        <v>637348</v>
       </c>
       <c r="R8" t="n">
-        <v>7012947</v>
+        <v>7012973</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1483,22 +1439,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,87 +1463,90 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016324</t>
+          <t>https://artportalen.se/Sighting/137132762</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>137016323</v>
+        <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>58164</v>
+        <v>92124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103023</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>637383</v>
+        <v>637433</v>
       </c>
       <c r="R9" t="n">
-        <v>7012955</v>
+        <v>7013000</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1611,22 +1570,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>16:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1635,33 +1594,49 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016323</t>
+          <t>https://artportalen.se/Sighting/137132770</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>137016317</v>
+        <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>99362</v>
+        <v>92138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1669,50 +1644,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1204</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>637356</v>
+        <v>637372</v>
       </c>
       <c r="R10" t="n">
-        <v>7012777</v>
+        <v>7012821</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1739,22 +1698,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,7 +1722,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1775,69 +1733,57 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016317</t>
+          <t>https://artportalen.se/Sighting/137124364</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>137016322</v>
+        <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>99362</v>
+        <v>92145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>637330</v>
+        <v>637421</v>
       </c>
       <c r="R11" t="n">
-        <v>7012744</v>
+        <v>7012891</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1869,7 +1815,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1879,7 +1825,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>13:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,7 +1834,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1906,70 +1851,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016322</t>
+          <t>https://artportalen.se/Sighting/137016314</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>137016355</v>
+        <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>99362</v>
+        <v>92087</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>637386</v>
+        <v>637357</v>
       </c>
       <c r="R12" t="n">
-        <v>7012951</v>
+        <v>7012776</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1998,7 +1927,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2008,7 +1937,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2017,88 +1946,71 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016355</t>
+          <t>https://artportalen.se/Sighting/137016319</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>137016357</v>
+        <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>99362</v>
+        <v>92087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>637371</v>
+        <v>637358</v>
       </c>
       <c r="R13" t="n">
-        <v>7012946</v>
+        <v>7012922</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2122,22 +2034,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2146,25 +2058,3819 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137124357</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>137016313</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>637421</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7012891</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016313</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>137124355</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>637398</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7012943</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124355</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>137124367</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>637303</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7012769</v>
+      </c>
+      <c r="S16" t="n">
+        <v>3</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124367</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>137132759</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>637342</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7012965</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132759</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>137132765</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>637350</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7012872</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132765</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>137132766</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>637356</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7012845</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132766</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137132769</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>637301</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7012807</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132769</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137016315</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80598</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>637352</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7012807</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016315</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137016320</v>
+      </c>
+      <c r="B22" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>637351</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7012753</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016320</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137124359</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>637365</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7012951</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124359</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137132767</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58005</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>637378</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7012834</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132767</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137124360</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>637357</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7012951</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124360</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137124362</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>637323</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7012907</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124362</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>137124363</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>637306</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7012873</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124363</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>137132758</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58008</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>637335</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7012959</v>
+      </c>
+      <c r="S28" t="n">
+        <v>5</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132758</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>137124356</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57186</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>637358</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7012912</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>07:22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124356</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>137016324</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>637373</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7012947</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016324</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>137147259</v>
+      </c>
+      <c r="B31" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Väster-Tvärtjärnen, Överlännäs s:n, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>637358</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7012912</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>07:50</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137147259</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>137016323</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58164</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>637383</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7012955</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016323</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>137016317</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>637356</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7012777</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>14:19</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016317</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>137016322</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>637330</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7012744</v>
+      </c>
+      <c r="S34" t="n">
+        <v>3</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016322</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>137016355</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>637386</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7012951</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137016355</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>137016357</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>637371</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7012946</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/137016357</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>137124368</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>390</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>637322</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7012782</v>
+      </c>
+      <c r="S37" t="n">
+        <v>3</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124368</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>137124369</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>637314</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7012805</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Markus Borja, Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137124369</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>137132756</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>637375</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7012928</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132756</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>137132757</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99368</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>637371</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7012923</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="inlineStr"/>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132757</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>137132760</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98230</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>637342</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7012970</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132760</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>137132768</v>
+      </c>
+      <c r="B42" t="n">
+        <v>79241</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>637392</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7012827</v>
+      </c>
+      <c r="S42" t="n">
+        <v>5</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:47</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF42" t="inlineStr"/>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja, Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132768</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>137132764</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79506</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>637336</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7012874</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="inlineStr"/>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132764</t>
         </is>
       </c>
     </row>
@@ -2182,6 +5888,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>137016317</v>
       </c>
       <c r="B33" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137016322</v>
       </c>
       <c r="B34" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>137016355</v>
       </c>
       <c r="B35" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>137016357</v>
       </c>
       <c r="B36" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>137124368</v>
       </c>
       <c r="B37" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>137124369</v>
       </c>
       <c r="B38" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>137132756</v>
       </c>
       <c r="B39" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>137132757</v>
       </c>
       <c r="B40" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>137132760</v>
       </c>
       <c r="B41" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137132768</v>
       </c>
       <c r="B42" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>137132764</v>
       </c>
       <c r="B43" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -4498,7 +4498,7 @@
         <v>137016317</v>
       </c>
       <c r="B33" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137016322</v>
       </c>
       <c r="B34" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>137016355</v>
       </c>
       <c r="B35" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>137016357</v>
       </c>
       <c r="B36" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>137124368</v>
       </c>
       <c r="B37" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>137124369</v>
       </c>
       <c r="B38" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>137132756</v>
       </c>
       <c r="B39" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>137132757</v>
       </c>
       <c r="B40" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>137132760</v>
       </c>
       <c r="B41" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>137016317</v>
       </c>
       <c r="B33" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137016322</v>
       </c>
       <c r="B34" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>137016355</v>
       </c>
       <c r="B35" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>137016357</v>
       </c>
       <c r="B36" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>137124368</v>
       </c>
       <c r="B37" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>137124369</v>
       </c>
       <c r="B38" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>137132756</v>
       </c>
       <c r="B39" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>137132757</v>
       </c>
       <c r="B40" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>137132760</v>
       </c>
       <c r="B41" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137132768</v>
       </c>
       <c r="B42" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>137132764</v>
       </c>
       <c r="B43" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>137016320</v>
       </c>
       <c r="B22" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>137124359</v>
       </c>
       <c r="B23" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>137132767</v>
       </c>
       <c r="B24" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>137124360</v>
       </c>
       <c r="B25" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>137124362</v>
       </c>
       <c r="B26" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>137124363</v>
       </c>
       <c r="B27" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>137132758</v>
       </c>
       <c r="B28" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>137124356</v>
       </c>
       <c r="B29" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137016324</v>
       </c>
       <c r="B30" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>137147259</v>
       </c>
       <c r="B31" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137016323</v>
       </c>
       <c r="B32" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>137016317</v>
       </c>
       <c r="B33" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137016322</v>
       </c>
       <c r="B34" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>137016355</v>
       </c>
       <c r="B35" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>137016357</v>
       </c>
       <c r="B36" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>137124368</v>
       </c>
       <c r="B37" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>137124369</v>
       </c>
       <c r="B38" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>137132756</v>
       </c>
       <c r="B39" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>137132757</v>
       </c>
       <c r="B40" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>137132760</v>
       </c>
       <c r="B41" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137132768</v>
       </c>
       <c r="B42" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>137132764</v>
       </c>
       <c r="B43" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3134,7 +3134,7 @@
         <v>137016320</v>
       </c>
       <c r="B22" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>137124359</v>
       </c>
       <c r="B23" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3374,7 +3374,7 @@
         <v>137132767</v>
       </c>
       <c r="B24" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3494,7 +3494,7 @@
         <v>137124360</v>
       </c>
       <c r="B25" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3619,7 +3619,7 @@
         <v>137124362</v>
       </c>
       <c r="B26" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>137124363</v>
       </c>
       <c r="B27" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>137132758</v>
       </c>
       <c r="B28" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>137124356</v>
       </c>
       <c r="B29" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4118,7 +4118,7 @@
         <v>137016324</v>
       </c>
       <c r="B30" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4246,7 +4246,7 @@
         <v>137147259</v>
       </c>
       <c r="B31" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>137016323</v>
       </c>
       <c r="B32" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4498,7 +4498,7 @@
         <v>137016317</v>
       </c>
       <c r="B33" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
         <v>137016322</v>
       </c>
       <c r="B34" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4752,7 +4752,7 @@
         <v>137016355</v>
       </c>
       <c r="B35" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>137016357</v>
       </c>
       <c r="B36" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>137124368</v>
       </c>
       <c r="B37" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>137124369</v>
       </c>
       <c r="B38" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>137132756</v>
       </c>
       <c r="B39" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5387,7 +5387,7 @@
         <v>137132757</v>
       </c>
       <c r="B40" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5516,7 +5516,7 @@
         <v>137132760</v>
       </c>
       <c r="B41" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>137132768</v>
       </c>
       <c r="B42" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5744,7 +5744,7 @@
         <v>137132764</v>
       </c>
       <c r="B43" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -3026,11 +3026,7 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3162,11 +3158,7 @@
       <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3282,11 +3274,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3402,11 +3390,7 @@
       <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3522,11 +3506,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3647,11 +3627,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3772,11 +3748,7 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3897,11 +3869,7 @@
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -4022,11 +3990,7 @@
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -4150,11 +4114,7 @@
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4274,11 +4234,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
           <t>passiv ljudinspelning</t>
@@ -4402,11 +4358,7 @@
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -4533,11 +4485,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
@@ -4787,11 +4735,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
@@ -4916,11 +4860,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
@@ -5293,11 +5233,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
@@ -5422,11 +5358,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
@@ -5771,11 +5703,7 @@
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ43"/>
+  <dimension ref="A1:AZ44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4079,10 +4079,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>137016324</v>
+        <v>137278106</v>
       </c>
       <c r="B30" t="n">
-        <v>58184</v>
+        <v>57864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4090,49 +4090,45 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>102621</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stortannsjön, Ång</t>
+          <t>Stortannsjön, Väster-Tvärtjärnen, Överlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>637373</v>
+        <v>637358</v>
       </c>
       <c r="R30" t="n">
-        <v>7012947</v>
+        <v>7012912</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4156,22 +4152,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:52</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4197,13 +4193,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016324</t>
+          <t>https://artportalen.se/Sighting/137278106</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>137147259</v>
+        <v>137016324</v>
       </c>
       <c r="B31" t="n">
         <v>58184</v>
@@ -4231,28 +4227,32 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stortannsjön, Väster-Tvärtjärnen, Överlännäs s:n, Ång</t>
+          <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>637358</v>
+        <v>637373</v>
       </c>
       <c r="R31" t="n">
-        <v>7012912</v>
+        <v>7012947</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4276,22 +4276,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>07:50</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>07:51</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4317,66 +4317,62 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137147259</t>
+          <t>https://artportalen.se/Sighting/137016324</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>137016323</v>
+        <v>137147259</v>
       </c>
       <c r="B32" t="n">
-        <v>58179</v>
+        <v>58184</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr">
         <is>
-          <t>observerad</t>
+          <t>passiv ljudinspelning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stortannsjön, Ång</t>
+          <t>Stortannsjön, Väster-Tvärtjärnen, Överlännäs s:n, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>637383</v>
+        <v>637358</v>
       </c>
       <c r="R32" t="n">
-        <v>7012955</v>
+        <v>7012912</v>
       </c>
       <c r="S32" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4400,22 +4396,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>07:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:24</t>
+          <t>07:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4441,63 +4437,63 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016323</t>
+          <t>https://artportalen.se/Sighting/137147259</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>137016317</v>
+        <v>137016323</v>
       </c>
       <c r="B33" t="n">
-        <v>99391</v>
+        <v>58179</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>637356</v>
+        <v>637383</v>
       </c>
       <c r="R33" t="n">
-        <v>7012777</v>
+        <v>7012955</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -4529,7 +4525,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4539,7 +4535,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:19</t>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4548,7 +4544,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4560,22 +4555,22 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016317</t>
+          <t>https://artportalen.se/Sighting/137016323</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>137016322</v>
+        <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4602,7 +4597,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>705</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4619,10 +4614,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>637330</v>
+        <v>637356</v>
       </c>
       <c r="R34" t="n">
-        <v>7012744</v>
+        <v>7012777</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4654,7 +4649,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4664,7 +4659,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>14:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4685,22 +4680,22 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016322</t>
+          <t>https://artportalen.se/Sighting/137016317</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>137016355</v>
+        <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4727,7 +4722,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>175</t>
+          <t>85</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -4744,13 +4739,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>637386</v>
+        <v>637330</v>
       </c>
       <c r="R35" t="n">
-        <v>7012951</v>
+        <v>7012744</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4779,7 +4774,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4789,7 +4784,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4805,27 +4800,27 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016355</t>
+          <t>https://artportalen.se/Sighting/137016322</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>137016357</v>
+        <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4852,7 +4847,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>175</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -4869,10 +4864,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>637371</v>
+        <v>637386</v>
       </c>
       <c r="R36" t="n">
-        <v>7012946</v>
+        <v>7012951</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4904,7 +4899,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4914,7 +4909,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4941,16 +4936,16 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137016357</t>
+          <t>https://artportalen.se/Sighting/137016355</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>137124368</v>
+        <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4977,7 +4972,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>64</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4994,13 +4989,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>637322</v>
+        <v>637371</v>
       </c>
       <c r="R37" t="n">
-        <v>7012782</v>
+        <v>7012946</v>
       </c>
       <c r="S37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5024,22 +5019,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:23</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5048,33 +5043,34 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137124368</t>
+          <t>https://artportalen.se/Sighting/137016357</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>137124369</v>
+        <v>137124368</v>
       </c>
       <c r="B38" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5101,7 +5097,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>390</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -5118,10 +5114,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>637314</v>
+        <v>637322</v>
       </c>
       <c r="R38" t="n">
-        <v>7012805</v>
+        <v>7012782</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -5153,7 +5149,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5163,7 +5159,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5189,16 +5185,16 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137124369</t>
+          <t>https://artportalen.se/Sighting/137124368</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>137132756</v>
+        <v>137124369</v>
       </c>
       <c r="B39" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5225,7 +5221,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5242,13 +5238,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>637375</v>
+        <v>637314</v>
       </c>
       <c r="R39" t="n">
-        <v>7012928</v>
+        <v>7012805</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5277,7 +5273,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5287,7 +5283,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5296,34 +5292,33 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Markus Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132756</t>
+          <t>https://artportalen.se/Sighting/137124369</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>137132757</v>
+        <v>137132756</v>
       </c>
       <c r="B40" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5350,7 +5345,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>57</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5367,10 +5362,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>637371</v>
+        <v>637375</v>
       </c>
       <c r="R40" t="n">
-        <v>7012923</v>
+        <v>7012928</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5402,7 +5397,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5412,7 +5407,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5439,51 +5434,63 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132757</t>
+          <t>https://artportalen.se/Sighting/137132756</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137132760</v>
+        <v>137132757</v>
       </c>
       <c r="B41" t="n">
-        <v>98253</v>
+        <v>99394</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>637342</v>
+        <v>637371</v>
       </c>
       <c r="R41" t="n">
-        <v>7012970</v>
+        <v>7012923</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5515,7 +5522,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5525,7 +5532,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5534,6 +5541,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5545,60 +5553,57 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132760</t>
+          <t>https://artportalen.se/Sighting/137132757</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>137132768</v>
+        <v>137132760</v>
       </c>
       <c r="B42" t="n">
-        <v>79261</v>
+        <v>98256</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Stortannsjön, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>637392</v>
+        <v>637342</v>
       </c>
       <c r="R42" t="n">
-        <v>7012827</v>
+        <v>7012970</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5630,7 +5635,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5640,7 +5645,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:47</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5649,7 +5654,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5661,22 +5665,22 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja, Markus Borja</t>
+          <t>Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137132768</t>
+          <t>https://artportalen.se/Sighting/137132760</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>137132764</v>
+        <v>137132768</v>
       </c>
       <c r="B43" t="n">
-        <v>79526</v>
+        <v>79261</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5684,21 +5688,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5711,10 +5715,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>637336</v>
+        <v>637392</v>
       </c>
       <c r="R43" t="n">
-        <v>7012874</v>
+        <v>7012827</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5746,7 +5750,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5756,7 +5760,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5769,21 +5773,6 @@
       <c r="AG43" t="b">
         <v>0</v>
       </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
@@ -5792,11 +5781,142 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Ann-Christine Borja</t>
+          <t>Ann-Christine Borja, Markus Borja</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137132768</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>137132764</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79526</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Stortannsjön, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>637336</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7012874</v>
+      </c>
+      <c r="S44" t="n">
+        <v>5</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Boteå</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="inlineStr"/>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Ann-Christine Borja</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/137132764</t>
         </is>
@@ -5846,6 +5966,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>137016320</v>
       </c>
       <c r="B22" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>137124359</v>
       </c>
       <c r="B23" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>137132767</v>
       </c>
       <c r="B24" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>137124360</v>
       </c>
       <c r="B25" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>137124362</v>
       </c>
       <c r="B26" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>137124363</v>
       </c>
       <c r="B27" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>137132758</v>
       </c>
       <c r="B28" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137124356</v>
       </c>
       <c r="B29" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>137278106</v>
       </c>
       <c r="B30" t="n">
-        <v>57864</v>
+        <v>57874</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>137016324</v>
       </c>
       <c r="B31" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>137147259</v>
       </c>
       <c r="B32" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>137016323</v>
       </c>
       <c r="B33" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137124368</v>
       </c>
       <c r="B38" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137124369</v>
       </c>
       <c r="B39" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137132756</v>
       </c>
       <c r="B40" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>137132757</v>
       </c>
       <c r="B41" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137132760</v>
       </c>
       <c r="B42" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>137132768</v>
       </c>
       <c r="B43" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137132764</v>
       </c>
       <c r="B44" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137124368</v>
       </c>
       <c r="B38" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137124369</v>
       </c>
       <c r="B39" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137132756</v>
       </c>
       <c r="B40" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>137132757</v>
       </c>
       <c r="B41" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137132760</v>
       </c>
       <c r="B42" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>137016320</v>
       </c>
       <c r="B22" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>137124359</v>
       </c>
       <c r="B23" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>137132767</v>
       </c>
       <c r="B24" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>137124360</v>
       </c>
       <c r="B25" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>137124362</v>
       </c>
       <c r="B26" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>137124363</v>
       </c>
       <c r="B27" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>137132758</v>
       </c>
       <c r="B28" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137124356</v>
       </c>
       <c r="B29" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>137278106</v>
       </c>
       <c r="B30" t="n">
-        <v>57874</v>
+        <v>57875</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>137016324</v>
       </c>
       <c r="B31" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>137147259</v>
       </c>
       <c r="B32" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>137016323</v>
       </c>
       <c r="B33" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137124368</v>
       </c>
       <c r="B38" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137124369</v>
       </c>
       <c r="B39" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137132756</v>
       </c>
       <c r="B40" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>137132757</v>
       </c>
       <c r="B41" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137132760</v>
       </c>
       <c r="B42" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>137132768</v>
       </c>
       <c r="B43" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137132764</v>
       </c>
       <c r="B44" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137124368</v>
       </c>
       <c r="B38" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137124369</v>
       </c>
       <c r="B39" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137132756</v>
       </c>
       <c r="B40" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>137132757</v>
       </c>
       <c r="B41" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137132760</v>
       </c>
       <c r="B42" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>137016320</v>
       </c>
       <c r="B22" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>137124359</v>
       </c>
       <c r="B23" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>137132767</v>
       </c>
       <c r="B24" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>137124360</v>
       </c>
       <c r="B25" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>137124362</v>
       </c>
       <c r="B26" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>137124363</v>
       </c>
       <c r="B27" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>137132758</v>
       </c>
       <c r="B28" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>137278106</v>
       </c>
       <c r="B30" t="n">
-        <v>57875</v>
+        <v>57876</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>137016324</v>
       </c>
       <c r="B31" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>137147259</v>
       </c>
       <c r="B32" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>137016323</v>
       </c>
       <c r="B33" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137124368</v>
       </c>
       <c r="B38" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137124369</v>
       </c>
       <c r="B39" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137132756</v>
       </c>
       <c r="B40" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>137132757</v>
       </c>
       <c r="B41" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137132760</v>
       </c>
       <c r="B42" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>137132768</v>
       </c>
       <c r="B43" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137132764</v>
       </c>
       <c r="B44" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137124368</v>
       </c>
       <c r="B38" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137124369</v>
       </c>
       <c r="B39" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137132756</v>
       </c>
       <c r="B40" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>137132757</v>
       </c>
       <c r="B41" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137132760</v>
       </c>
       <c r="B42" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>137132768</v>
       </c>
       <c r="B43" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137132764</v>
       </c>
       <c r="B44" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137124368</v>
       </c>
       <c r="B38" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137124369</v>
       </c>
       <c r="B39" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137132756</v>
       </c>
       <c r="B40" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>137132757</v>
       </c>
       <c r="B41" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137132760</v>
       </c>
       <c r="B42" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>137132768</v>
       </c>
       <c r="B43" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137132764</v>
       </c>
       <c r="B44" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4570,7 +4570,7 @@
         <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
+          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4695,7 +4695,7 @@
         <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137124368</v>
       </c>
       <c r="B38" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137124369</v>
       </c>
       <c r="B39" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137132756</v>
       </c>
       <c r="B40" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>137132757</v>
       </c>
       <c r="B41" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137132760</v>
       </c>
       <c r="B42" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>137132768</v>
       </c>
       <c r="B43" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137132764</v>
       </c>
       <c r="B44" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -3115,7 +3115,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -4680,7 +4680,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Markus Borja, Diego Borja, Ann-Christine Borja</t>
+          <t>Markus Borja, Ann-Christine Borja, Diego Borja</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92206</v>
+        <v>92207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92148</v>
+        <v>92149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79535</v>
+        <v>79536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80650</v>
+        <v>80651</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>

--- a/artfynd/A 35041-2025 artfynd.xlsx
+++ b/artfynd/A 35041-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137124361</v>
       </c>
       <c r="B2" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137124366</v>
       </c>
       <c r="B3" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137132761</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>137016321</v>
       </c>
       <c r="B5" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>137124358</v>
       </c>
       <c r="B6" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>137124365</v>
       </c>
       <c r="B7" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>137132762</v>
       </c>
       <c r="B8" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>137132770</v>
       </c>
       <c r="B9" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>137124364</v>
       </c>
       <c r="B10" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>137016314</v>
       </c>
       <c r="B11" t="n">
-        <v>92207</v>
+        <v>92210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1860,7 +1860,7 @@
         <v>137016319</v>
       </c>
       <c r="B12" t="n">
-        <v>92149</v>
+        <v>92152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1972,7 +1972,7 @@
         <v>137124357</v>
       </c>
       <c r="B13" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         <v>137016313</v>
       </c>
       <c r="B14" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>137124355</v>
       </c>
       <c r="B15" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>137124367</v>
       </c>
       <c r="B16" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137132759</v>
       </c>
       <c r="B17" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>137132765</v>
       </c>
       <c r="B18" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>137132766</v>
       </c>
       <c r="B19" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>137132769</v>
       </c>
       <c r="B20" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2999,7 +2999,7 @@
         <v>137016315</v>
       </c>
       <c r="B21" t="n">
-        <v>80651</v>
+        <v>80654</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
         <v>137016320</v>
       </c>
       <c r="B22" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>137124359</v>
       </c>
       <c r="B23" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>137132767</v>
       </c>
       <c r="B24" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3478,7 +3478,7 @@
         <v>137124360</v>
       </c>
       <c r="B25" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>137124362</v>
       </c>
       <c r="B26" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>137124363</v>
       </c>
       <c r="B27" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3841,7 +3841,7 @@
         <v>137132758</v>
       </c>
       <c r="B28" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3962,7 +3962,7 @@
         <v>137124356</v>
       </c>
       <c r="B29" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4082,7 +4082,7 @@
         <v>137278106</v>
       </c>
       <c r="B30" t="n">
-        <v>57876</v>
+        <v>57879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4202,7 +4202,7 @@
         <v>137016324</v>
       </c>
       <c r="B31" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>137147259</v>
       </c>
       <c r="B32" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>137016323</v>
       </c>
       <c r="B33" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>137016317</v>
       </c>
       <c r="B34" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4695,7 +4695,7 @@
         <v>137016322</v>
       </c>
       <c r="B35" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4820,7 +4820,7 @@
         <v>137016355</v>
       </c>
       <c r="B36" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4945,7 +4945,7 @@
         <v>137016357</v>
       </c>
       <c r="B37" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5070,7 +5070,7 @@
         <v>137124368</v>
       </c>
       <c r="B38" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137124369</v>
       </c>
       <c r="B39" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>137132756</v>
       </c>
       <c r="B40" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5443,7 +5443,7 @@
         <v>137132757</v>
       </c>
       <c r="B41" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5568,7 +5568,7 @@
         <v>137132760</v>
       </c>
       <c r="B42" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>137132768</v>
       </c>
       <c r="B43" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5796,7 +5796,7 @@
         <v>137132764</v>
       </c>
       <c r="B44" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
